--- a/Treinamento/IndexacaoFG/Arquivos/Bloqueios Honda 18.11.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Bloqueios Honda 18.11.2025.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/thaiana_felipe_allianz_com_br/Documents/HONDA RECUSAS/BLOQUEIOS HONDA/NOVEMBRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96C3EC5B-F0E3-4838-AA1C-1B67622B073F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6322808-ED78-4501-A4E3-D01BEB245F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{49E03E13-C02B-453A-87EF-14C60E074F4A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{49E03E13-C02B-453A-87EF-14C60E074F4A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bloqueios 17.11.2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Bloqueios 18.11.2025" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloqueios 17.11.2025'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bloqueios 18.11.2025'!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="39">
   <si>
     <t>NR PROPOSTA</t>
   </si>
@@ -95,58 +95,67 @@
     <t>Vistoria Presencial</t>
   </si>
   <si>
-    <t xml:space="preserve">WAGNER DA SILVA SANTOS                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARINALVA PEREIRA DE SOUZA                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVONILSON SOARES LIMA                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CINTIA QUEIROZ SOBRINHO                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RONDINELLY MOREIRA SANTOS                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANDRESA SANTOS VIEIRA                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELISANGELA MARIA DA SILVA                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOAO FABRICIO DE JESUS FERREIRA              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JENICLEIDE SANTOS PINHEIRO                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARIANE MORAIS DO NASCIMENTO RIBEIRO          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOEL PIRES DOS REIS                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FATIMA CRISTINA MOTA BORDINO                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARMILTON SANTOS DE OLIVEIRA                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAIQUE DA SILVA BARBOSA                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOSINEIDE DE OLIVEIRA PEREIRA MEDEIROS       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">             75,29-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Endosso    </t>
   </si>
   <si>
-    <t xml:space="preserve">MAIARA SANTOS OLIVEIRA                       </t>
+    <t xml:space="preserve">RONNER MULLER LIMA BRAGA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">              2,61-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS FELIPE DE ALMEIDA SOUSA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO MANOEL BENEDITO DA SILVA FILHO       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIMARA NUNES DOS SANTOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRISCILA DA SILVA SOUSA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACELIO LIMA CARVALHO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OZIEL BERNARDO DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORLANDO JOSE DA COSTA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA DOS SANTOS DA HORA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREIA ARAUJO DE SOUSA RODRIGUES            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHELLE LIMA VASCONCELOS PINTO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL PEREIRA DOS SANTOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS HENRIQUE FAGUNDES NETO JUNIOR         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERCIA MENDONCA DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNIO EVANGELISTA DA SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDEMI ALVES CORREIA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WESLEY RUFINO DO NASCIMENTO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIANA PEREIRA DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODILIR PEREIRA LINS                          </t>
   </si>
 </sst>
 </file>
@@ -565,7 +574,7 @@
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
     <col min="2" max="2" width="24.1796875" customWidth="1"/>
     <col min="3" max="3" width="41.453125" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
     <col min="6" max="6" width="15.81640625" customWidth="1"/>
     <col min="12" max="12" width="18.1796875" customWidth="1"/>
     <col min="13" max="13" width="13.26953125" customWidth="1"/>
@@ -611,31 +620,31 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>135417618</v>
+        <v>130964511</v>
       </c>
       <c r="B2" s="3">
-        <v>1879414759</v>
+        <v>82850607304</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1212</v>
+      </c>
+      <c r="F2" s="4">
+        <v>45979</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3">
-        <v>6877.35</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1211</v>
-      </c>
-      <c r="F2" s="4">
-        <v>45978</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="I2" s="3">
-        <v>4015856</v>
+        <v>4015124</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -649,78 +658,78 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>135419298</v>
+        <v>135438959</v>
       </c>
       <c r="B3" s="3">
-        <v>26890755553</v>
+        <v>45278314885</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3">
-        <v>427.21</v>
+        <v>1165.6099999999999</v>
       </c>
       <c r="E3" s="3">
         <v>1212</v>
       </c>
       <c r="F3" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="3">
-        <v>4015559</v>
+        <v>4015117</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K3" s="3">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>135426827</v>
+        <v>135439729</v>
       </c>
       <c r="B4" s="3">
-        <v>93929790530</v>
+        <v>7044622496</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3">
-        <v>1332.97</v>
+        <v>692</v>
       </c>
       <c r="E4" s="3">
         <v>1212</v>
       </c>
       <c r="F4" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="3">
-        <v>4015436</v>
+        <v>4015856</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K4" s="3">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -728,40 +737,40 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>135421110</v>
+        <v>135438590</v>
       </c>
       <c r="B5" s="3">
-        <v>27834682806</v>
+        <v>5414874506</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3">
-        <v>2914.14</v>
+        <v>2138.9</v>
       </c>
       <c r="E5" s="3">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F5" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="3">
-        <v>4015856</v>
+        <v>4015437</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K5" s="3">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -769,40 +778,40 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>135432800</v>
+        <v>135444710</v>
       </c>
       <c r="B6" s="3">
-        <v>51188244</v>
+        <v>10663802440</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3">
-        <v>4641.8500000000004</v>
+        <v>1298.1500000000001</v>
       </c>
       <c r="E6" s="3">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F6" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I6" s="3">
-        <v>4015721</v>
+        <v>4015532</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K6" s="3">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -810,31 +819,31 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>135421266</v>
+        <v>135446005</v>
       </c>
       <c r="B7" s="3">
-        <v>748974547</v>
+        <v>13781497771</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>699.18</v>
+        <v>1176.1400000000001</v>
       </c>
       <c r="E7" s="3">
         <v>1212</v>
       </c>
       <c r="F7" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I7" s="3">
-        <v>4015055</v>
+        <v>4015607</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -851,31 +860,31 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>135422150</v>
+        <v>135446789</v>
       </c>
       <c r="B8" s="3">
-        <v>8537834467</v>
+        <v>2376521459</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>383.27</v>
+        <v>2044.84</v>
       </c>
       <c r="E8" s="3">
         <v>1212</v>
       </c>
       <c r="F8" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I8" s="3">
-        <v>4015446</v>
+        <v>4015544</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -892,22 +901,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>135423038</v>
+        <v>135446284</v>
       </c>
       <c r="B9" s="3">
-        <v>77738268549</v>
+        <v>45981850400</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3">
-        <v>526.23</v>
+        <v>1541.6</v>
       </c>
       <c r="E9" s="3">
         <v>1212</v>
       </c>
       <c r="F9" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>16</v>
@@ -916,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="I9" s="3">
-        <v>4015436</v>
+        <v>4015544</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -933,40 +942,40 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>135430598</v>
+        <v>135453390</v>
       </c>
       <c r="B10" s="3">
-        <v>5929361550</v>
+        <v>6314028108</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3">
-        <v>2453.9299999999998</v>
+        <v>590.30999999999995</v>
       </c>
       <c r="E10" s="3">
         <v>1212</v>
       </c>
       <c r="F10" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I10" s="3">
-        <v>4015095</v>
+        <v>4015576</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K10" s="3">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -974,31 +983,31 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>135424643</v>
+        <v>135446829</v>
       </c>
       <c r="B11" s="3">
-        <v>908015127</v>
+        <v>8241818750</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3">
-        <v>526.44000000000005</v>
+        <v>634.91</v>
       </c>
       <c r="E11" s="3">
         <v>1212</v>
       </c>
       <c r="F11" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I11" s="3">
-        <v>4015332</v>
+        <v>4015050</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -1015,22 +1024,22 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>135425879</v>
+        <v>135449007</v>
       </c>
       <c r="B12" s="3">
-        <v>520819900</v>
+        <v>93273576200</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D12" s="3">
-        <v>2079.5300000000002</v>
+        <v>989.13</v>
       </c>
       <c r="E12" s="3">
         <v>1212</v>
       </c>
       <c r="F12" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>16</v>
@@ -1039,16 +1048,16 @@
         <v>12</v>
       </c>
       <c r="I12" s="3">
-        <v>4015696</v>
+        <v>4015576</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K12" s="3">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -1056,31 +1065,31 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>135429497</v>
+        <v>135449394</v>
       </c>
       <c r="B13" s="3">
-        <v>5642889850</v>
+        <v>13357385686</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13" s="3">
-        <v>500.94</v>
+        <v>1533.22</v>
       </c>
       <c r="E13" s="3">
         <v>1212</v>
       </c>
       <c r="F13" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I13" s="3">
-        <v>4015196</v>
+        <v>4015425</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
@@ -1097,22 +1106,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>135429710</v>
+        <v>135449948</v>
       </c>
       <c r="B14" s="3">
-        <v>5028315531</v>
+        <v>1067994106</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3">
-        <v>869.2</v>
+        <v>1564.64</v>
       </c>
       <c r="E14" s="3">
         <v>1212</v>
       </c>
       <c r="F14" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>15</v>
@@ -1121,7 +1130,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="3">
-        <v>4015583</v>
+        <v>4015123</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -1138,22 +1147,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>135433511</v>
+        <v>135450368</v>
       </c>
       <c r="B15" s="3">
-        <v>8262296460</v>
+        <v>1544639570</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" s="3">
-        <v>554.55999999999995</v>
+        <v>570.41</v>
       </c>
       <c r="E15" s="3">
         <v>1212</v>
       </c>
       <c r="F15" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -1162,16 +1171,16 @@
         <v>12</v>
       </c>
       <c r="I15" s="3">
-        <v>4015535</v>
+        <v>4015532</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="K15" s="3">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1179,31 +1188,31 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>133738240</v>
+        <v>135451939</v>
       </c>
       <c r="B16" s="3">
-        <v>4426552400</v>
+        <v>2882010192</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1184.79</v>
       </c>
       <c r="E16" s="3">
         <v>1212</v>
       </c>
       <c r="F16" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I16" s="3">
-        <v>4015397</v>
+        <v>4015611</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -1220,22 +1229,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>135435124</v>
+        <v>135451562</v>
       </c>
       <c r="B17" s="3">
-        <v>52987094272</v>
+        <v>62281399168</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="3">
-        <v>1866.11</v>
+        <v>1431.93</v>
       </c>
       <c r="E17" s="3">
         <v>1212</v>
       </c>
       <c r="F17" s="4">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>15</v>
@@ -1244,7 +1253,7 @@
         <v>12</v>
       </c>
       <c r="I17" s="3">
-        <v>4015585</v>
+        <v>4015123</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>13</v>
@@ -1260,52 +1269,124 @@
       <c r="O17" s="1"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="A18" s="3">
+        <v>135451706</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2779019956</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1047.73</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1212</v>
+      </c>
+      <c r="F18" s="4">
+        <v>45979</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4015275</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="3">
+        <v>717</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="A19" s="3">
+        <v>135452639</v>
+      </c>
+      <c r="B19" s="3">
+        <v>8465097763</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1064.04</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1212</v>
+      </c>
+      <c r="F19" s="4">
+        <v>45979</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="3">
+        <v>4015279</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="3">
+        <v>717</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="A20" s="3">
+        <v>135453526</v>
+      </c>
+      <c r="B20" s="3">
+        <v>24510033249</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1683.61</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1212</v>
+      </c>
+      <c r="F20" s="4">
+        <v>45979</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="3">
+        <v>4015577</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="3">
+        <v>715</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -1557,46 +1638,53 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517383</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-517383</Url>
-      <Description>QAFFA7D2F2TC-2102087286-517383</Description>
-    </_dlc_DocIdUrl>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1978,53 +2066,46 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-517383</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-517383</Url>
+      <Description>QAFFA7D2F2TC-2102087286-517383</Description>
+    </_dlc_DocIdUrl>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2037,13 +2118,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809F9E28-94E1-4EB1-B9AC-67B6780BD594}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34A3AA62-C449-41FA-A4AD-BF0DD43A488A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2069,9 +2146,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34A3AA62-C449-41FA-A4AD-BF0DD43A488A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809F9E28-94E1-4EB1-B9AC-67B6780BD594}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
